--- a/Configs/GameConfig/Datas/fg/#EntityProfile-实体档案.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EntityProfile-实体档案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3308,6 +3308,83 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fragment.era</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>16</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
